--- a/resampling/input/accessibility_reports_returned/IRC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/IRC_accessibility_report.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+  </numFmts>
   <fonts count="8">
     <font>
       <name val="Calibri"/>
@@ -110,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,6 +135,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -210,7 +213,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q75" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q85" headerRowCount="1">
   <autoFilter ref="A1:Q75"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="11" min="1" max="1"/>
@@ -856,8 +859,26 @@
       <c r="J2" t="n">
         <v>48</v>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -889,8 +910,26 @@
       <c r="J3" t="n">
         <v>35</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -922,8 +961,26 @@
       <c r="J4" t="n">
         <v>25</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -965,8 +1022,31 @@
       <c r="J5" t="n">
         <v>23</v>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1008,8 +1088,26 @@
       <c r="J6" t="n">
         <v>20</v>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1051,8 +1149,26 @@
       <c r="J7" t="n">
         <v>18</v>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1084,8 +1200,26 @@
       <c r="J8" t="n">
         <v>8</v>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1127,8 +1261,26 @@
       <c r="J9" t="n">
         <v>7</v>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1160,8 +1312,26 @@
       <c r="J10" t="n">
         <v>7</v>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1193,8 +1363,31 @@
       <c r="J11" t="n">
         <v>6</v>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1236,8 +1429,26 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1279,8 +1490,26 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1312,8 +1541,26 @@
       <c r="J14" t="n">
         <v>70</v>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1345,8 +1592,31 @@
       <c r="J15" t="n">
         <v>27</v>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1378,8 +1648,26 @@
       <c r="J16" t="n">
         <v>20</v>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1411,8 +1699,31 @@
       <c r="J17" t="n">
         <v>19</v>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1444,8 +1755,31 @@
       <c r="J18" t="n">
         <v>14</v>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1477,8 +1811,31 @@
       <c r="J19" t="n">
         <v>9</v>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1510,8 +1867,26 @@
       <c r="J20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1553,8 +1928,31 @@
       <c r="J21" t="n">
         <v>6</v>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1596,8 +1994,31 @@
       <c r="J22" t="n">
         <v>5</v>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1639,8 +2060,31 @@
       <c r="J23" t="n">
         <v>3</v>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1672,8 +2116,31 @@
       <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1705,8 +2172,26 @@
       <c r="J25" t="n">
         <v>23</v>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1738,8 +2223,26 @@
       <c r="J26" t="n">
         <v>19</v>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1771,8 +2274,26 @@
       <c r="J27" t="n">
         <v>15</v>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1804,8 +2325,26 @@
       <c r="J28" t="n">
         <v>9</v>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1847,8 +2386,26 @@
       <c r="J29" t="n">
         <v>8</v>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1880,8 +2437,26 @@
       <c r="J30" t="n">
         <v>7</v>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1913,8 +2488,26 @@
       <c r="J31" t="n">
         <v>6</v>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1956,8 +2549,26 @@
       <c r="J32" t="n">
         <v>6</v>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1989,8 +2600,26 @@
       <c r="J33" t="n">
         <v>5</v>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2032,8 +2661,26 @@
       <c r="J34" t="n">
         <v>4</v>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2075,8 +2722,6 @@
       <c r="J35" t="n">
         <v>0</v>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2108,8 +2753,31 @@
       <c r="J36" t="n">
         <v>110</v>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2141,8 +2809,31 @@
       <c r="J37" t="n">
         <v>24</v>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2174,8 +2865,31 @@
       <c r="J38" t="n">
         <v>19</v>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2207,8 +2921,31 @@
       <c r="J39" t="n">
         <v>12</v>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2250,8 +2987,31 @@
       <c r="J40" t="n">
         <v>12</v>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2283,8 +3043,31 @@
       <c r="J41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2316,8 +3099,31 @@
       <c r="J42" t="n">
         <v>7</v>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2349,8 +3155,31 @@
       <c r="J43" t="n">
         <v>5</v>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2382,8 +3211,31 @@
       <c r="J44" t="n">
         <v>5</v>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2415,8 +3267,31 @@
       <c r="J45" t="n">
         <v>3</v>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2458,8 +3333,31 @@
       <c r="J46" t="n">
         <v>72</v>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2491,8 +3389,31 @@
       <c r="J47" t="n">
         <v>32</v>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2524,8 +3445,31 @@
       <c r="J48" t="n">
         <v>24</v>
       </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2567,8 +3511,31 @@
       <c r="J49" t="n">
         <v>18</v>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2600,8 +3567,31 @@
       <c r="J50" t="n">
         <v>14</v>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2633,8 +3623,31 @@
       <c r="J51" t="n">
         <v>13</v>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2666,8 +3679,31 @@
       <c r="J52" t="n">
         <v>12</v>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2699,8 +3735,31 @@
       <c r="J53" t="n">
         <v>11</v>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2732,8 +3791,31 @@
       <c r="J54" t="n">
         <v>6</v>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2765,8 +3847,31 @@
       <c r="J55" t="n">
         <v>2</v>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2798,8 +3903,6 @@
       <c r="J56" t="n">
         <v>102</v>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2831,8 +3934,6 @@
       <c r="J57" t="n">
         <v>30</v>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2864,8 +3965,26 @@
       <c r="J58" t="n">
         <v>18</v>
       </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2897,8 +4016,26 @@
       <c r="J59" t="n">
         <v>15</v>
       </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2930,8 +4067,26 @@
       <c r="J60" t="n">
         <v>13</v>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2963,8 +4118,6 @@
       <c r="J61" t="n">
         <v>10</v>
       </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2996,8 +4149,6 @@
       <c r="J62" t="n">
         <v>7</v>
       </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3029,8 +4180,6 @@
       <c r="J63" t="n">
         <v>6</v>
       </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3072,8 +4221,26 @@
       <c r="J64" t="n">
         <v>3</v>
       </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3105,8 +4272,26 @@
       <c r="J65" t="n">
         <v>0</v>
       </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3138,8 +4323,31 @@
       <c r="J66" t="n">
         <v>62</v>
       </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3171,8 +4379,31 @@
       <c r="J67" t="n">
         <v>58</v>
       </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3204,8 +4435,26 @@
       <c r="J68" t="n">
         <v>27</v>
       </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3237,8 +4486,31 @@
       <c r="J69" t="n">
         <v>15</v>
       </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3270,8 +4542,31 @@
       <c r="J70" t="n">
         <v>12</v>
       </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3303,8 +4598,31 @@
       <c r="J71" t="n">
         <v>6</v>
       </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3336,8 +4654,31 @@
       <c r="J72" t="n">
         <v>6</v>
       </c>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3369,8 +4710,31 @@
       <c r="J73" t="n">
         <v>6</v>
       </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3402,8 +4766,31 @@
       <c r="J74" t="n">
         <v>6</v>
       </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Placeholder: partner marked inaccessible but did not provide a reason category on return (2026-09-13). Follow up needed.</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3445,22 +4832,438 @@
       <c r="J75" t="n">
         <v>0</v>
       </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Tsanni</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>5</v>
+      </c>
+      <c r="O76" s="14" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Jibia A</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="14" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Jibia B</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="14" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Salewa</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>6</v>
+      </c>
+      <c r="O79" s="14" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Keta</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>6</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>35</v>
+      </c>
+      <c r="O80" s="14" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Yankuzo B</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed.</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>3</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>8</v>
+      </c>
+      <c r="O81" s="14" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Arewa 2</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3</v>
+      </c>
+      <c r="O82" s="14" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Darini Magaji Abu</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Batsari</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>2</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>12</v>
+      </c>
+      <c r="O83" s="14" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Jamali</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Binji</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>6</v>
+      </c>
+      <c r="O84" s="14" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Mada</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-16 - not previously listed. This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>6</v>
+      </c>
+      <c r="O85" s="14" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="K2:K75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="5">
+    <dataValidation sqref="K2:K75 K76:K81 K82:K85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L75 L76:L81 L82:L85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P75 P76:P81 P82:P85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q75 Q76:Q81 Q82:Q85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O76:O81 O82:O85" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today." type="date" operator="between">
+      <formula1>2026-07-01</formula1>
+      <formula2>2026-09-16</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3614,8 +5417,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3658,8 +5459,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3702,8 +5501,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3746,8 +5543,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3790,8 +5585,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3834,8 +5627,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3878,8 +5669,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3922,8 +5711,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3961,8 +5748,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4000,8 +5785,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4039,8 +5822,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4078,8 +5859,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4117,8 +5896,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4156,8 +5933,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4195,8 +5970,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4234,8 +6007,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4273,8 +6044,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4312,8 +6081,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4351,8 +6118,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4390,8 +6155,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4429,8 +6192,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4473,8 +6234,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4517,8 +6276,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4561,8 +6318,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4605,8 +6360,6 @@
           <t>36</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4644,8 +6397,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4683,8 +6434,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4722,8 +6471,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4761,8 +6508,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4800,8 +6545,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4839,8 +6582,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4878,8 +6619,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4917,8 +6656,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4956,8 +6693,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4995,8 +6730,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5034,8 +6767,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5073,8 +6804,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5112,8 +6841,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5151,8 +6878,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5190,8 +6915,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5229,8 +6952,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5268,8 +6989,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5307,8 +7026,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5346,8 +7063,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5385,8 +7100,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5424,8 +7137,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5463,8 +7174,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5502,8 +7211,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5541,8 +7248,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5580,8 +7285,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5619,8 +7322,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5658,8 +7359,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5697,8 +7396,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5736,8 +7433,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5775,8 +7470,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5819,8 +7512,6 @@
           <t>102</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5858,8 +7549,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5897,8 +7586,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5936,8 +7623,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5975,8 +7660,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6014,8 +7697,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6053,8 +7734,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6092,8 +7771,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6131,8 +7808,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6170,8 +7845,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6209,8 +7882,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6248,8 +7919,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6287,8 +7956,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6326,8 +7993,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6370,8 +8035,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6414,8 +8077,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6458,8 +8119,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6502,8 +8161,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6541,8 +8198,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6580,8 +8235,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6619,8 +8272,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6658,8 +8309,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6697,8 +8346,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6736,8 +8383,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6775,8 +8420,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6814,8 +8457,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6853,8 +8494,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6892,8 +8531,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6931,8 +8568,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6970,8 +8605,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7009,8 +8642,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7048,8 +8679,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7087,8 +8716,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7126,8 +8753,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7170,8 +8795,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7214,8 +8837,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7258,8 +8879,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7302,8 +8921,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7341,8 +8958,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7380,8 +8995,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7419,8 +9032,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7458,8 +9069,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7497,8 +9106,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7536,8 +9143,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7575,8 +9180,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7614,8 +9217,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7653,8 +9254,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7692,8 +9291,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7731,8 +9328,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7770,8 +9365,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7809,8 +9402,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7848,8 +9439,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7887,8 +9476,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7926,8 +9513,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7970,8 +9555,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8014,8 +9597,6 @@
           <t>36</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8058,8 +9639,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8102,8 +9681,6 @@
           <t>42</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8141,8 +9718,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8180,8 +9755,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8219,8 +9792,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8258,8 +9829,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8297,8 +9866,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8336,8 +9903,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8375,8 +9940,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8414,8 +9977,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8453,8 +10014,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8492,8 +10051,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8531,8 +10088,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8674,8 +10229,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9007,13 +10560,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82521EF2-DCF0-47E9-B72A-3DF2EBE318B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C1B22D4-2D81-4DDD-8168-29144C8B46FD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC83CB6C-47F4-49DA-BB60-1A3CF4B778A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A4780-DB3B-4EA7-AEE3-4819D9B8F562}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92108CB6-918A-4E7E-AE1A-94A78576D2C6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{270225AC-FE5D-4E9A-A39A-A497E42665CF}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/IRC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/IRC_accessibility_report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -63,11 +63,13 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -91,12 +93,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B2A4A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002C5F8A"/>
+        <fgColor rgb="FF2C5F8A"/>
       </patternFill>
     </fill>
   </fills>
@@ -112,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,14 +125,13 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -213,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q85" headerRowCount="1">
-  <autoFilter ref="A1:Q75"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q146" headerRowCount="1">
+  <autoFilter ref="A1:Q146"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -234,7 +230,7 @@
     <tableColumn id="16" name="Reported by (Partner / IMPACT-default)"/>
     <tableColumn id="17" name="Source channel"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -258,7 +254,7 @@
     <tableColumn id="14" name="Reported by (Partner / IMPACT-default)"/>
     <tableColumn id="15" name="Source channel"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -554,26 +550,26 @@
   <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="30" customWidth="1" style="11" min="1" max="1"/>
-    <col width="95" customWidth="1" style="11" min="2" max="2"/>
+    <col width="30" customWidth="1" style="13" min="1" max="1"/>
+    <col width="95" customWidth="1" style="13" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="11">
+    <row r="1" ht="18" customHeight="1" s="13">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>IRC - NGA MSNA 2026 accessibility report</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.6" customHeight="1" s="11">
+    <row r="3" ht="15.6" customHeight="1" s="13">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1" s="11">
-      <c r="A4" s="10" t="inlineStr">
+    <row r="4" ht="90" customHeight="1" s="13">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>This file lists every ward (and, on the second sheet, every individual cluster) currently assigned to your organisation under the NGA MSNA 2026 sampling design, so you can tell us where your teams are having trouble collecting data and why. We use this to decide how to respond - drawing a replacement cluster where needed - and to correctly document, in our final reporting, which areas' we were able to collect from and which we weren't. Accurate, complete reporting from you feeds directly into that documentation.</t>
         </is>
@@ -586,74 +582,74 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15.6" customHeight="1" s="11">
+    <row r="8" ht="15.6" customHeight="1" s="13">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>What to do</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" s="11">
+    <row r="9" ht="60" customHeight="1" s="13">
       <c r="A9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Open the 'Ward Accessibility' sheet first - this is your main report, one row per ward you have clusters in. It's pre-filled with every ward/LGA combination assigned to you; you don't need to add or remove rows. Rows are sorted within each LGA by Total target HHs, largest first, so your main wards come before any small border cases.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1" s="11">
+    <row r="10" ht="60" customHeight="1" s="13">
       <c r="A10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" s="11">
+    <row r="11" ht="60" customHeight="1" s="13">
       <c r="A11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1" s="11">
+    <row r="12" ht="60" customHeight="1" s="13">
       <c r="A12" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1" s="11">
+    <row r="13" ht="60" customHeight="1" s="13">
       <c r="A13" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1" s="11">
+    <row r="14" ht="60" customHeight="1" s="13">
       <c r="A14" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="90" customHeight="1" s="11">
+    <row r="15" ht="90" customHeight="1" s="13">
       <c r="A15" s="5" t="n">
         <v>7</v>
       </c>
@@ -663,7 +659,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.6" customHeight="1" s="11">
+    <row r="17" ht="15.6" customHeight="1" s="13">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
@@ -682,25 +678,25 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="45" customHeight="1" s="11">
+    <row r="19" ht="45" customHeight="1" s="13">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Ward Accessibility</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1" s="11">
+    <row r="20" ht="45" customHeight="1" s="13">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -720,110 +716,108 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:Q146"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="14" customWidth="1" style="11" min="1" max="1"/>
-    <col width="14" customWidth="1" style="11" min="2" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="19" customWidth="1" style="11" min="4" max="4"/>
-    <col width="30" customWidth="1" style="11" min="5" max="5"/>
-    <col width="30" customWidth="1" style="11" min="6" max="6"/>
-    <col width="14" customWidth="1" style="11" min="7" max="7"/>
-    <col width="20" customWidth="1" style="11" min="8" max="8"/>
-    <col width="16" customWidth="1" style="11" min="9" max="9"/>
-    <col width="30" customWidth="1" style="11" min="10" max="10"/>
-    <col width="20" customWidth="1" style="11" min="11" max="11"/>
-    <col width="19" customWidth="1" style="11" min="12" max="12"/>
-    <col width="16" customWidth="1" style="11" min="13" max="13"/>
-    <col width="30" customWidth="1" style="11" min="14" max="14"/>
-    <col width="17" customWidth="1" style="11" min="15" max="15"/>
-    <col width="30" customWidth="1" style="11" min="16" max="16"/>
-    <col width="18" customWidth="1" style="11" min="17" max="17"/>
+    <col width="14" customWidth="1" style="13" min="1" max="2"/>
+    <col width="16" customWidth="1" style="13" min="3" max="3"/>
+    <col width="19" customWidth="1" style="13" min="4" max="4"/>
+    <col width="30" customWidth="1" style="13" min="5" max="6"/>
+    <col width="42" customWidth="1" style="13" min="7" max="7"/>
+    <col width="20" customWidth="1" style="13" min="8" max="8"/>
+    <col width="16" customWidth="1" style="13" min="9" max="9"/>
+    <col width="30" customWidth="1" style="13" min="10" max="10"/>
+    <col width="20" customWidth="1" style="13" min="11" max="11"/>
+    <col width="19" customWidth="1" style="13" min="12" max="12"/>
+    <col width="16" customWidth="1" style="13" min="13" max="13"/>
+    <col width="30" customWidth="1" style="13" min="14" max="14"/>
+    <col width="17" customWidth="1" style="13" min="15" max="15"/>
+    <col width="30" customWidth="1" style="13" min="16" max="16"/>
+    <col width="18" customWidth="1" style="13" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Ward (GRID3)</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Ward (OCHA/COD)</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Ward spans multiple LGAs (Y/N)</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Other LGA(s) sharing this ward</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Non-IDP clusters</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>IDP clusters</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Total target HHs (primary)</t>
         </is>
       </c>
-      <c r="K1" s="13" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Accessible (Y/N)</t>
         </is>
       </c>
-      <c r="L1" s="13" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>Reason category</t>
         </is>
       </c>
-      <c r="M1" s="13" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Reason notes</t>
         </is>
       </c>
-      <c r="N1" s="13" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>% of target achieved so far</t>
         </is>
       </c>
-      <c r="O1" s="13" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Date reported</t>
         </is>
       </c>
-      <c r="P1" s="13" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>Reported by (Partner / IMPACT-default)</t>
         </is>
       </c>
-      <c r="Q1" s="13" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>Source channel</t>
         </is>
@@ -2722,6 +2716,16 @@
       <c r="J35" t="n">
         <v>0</v>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3903,6 +3907,16 @@
       <c r="J56" t="n">
         <v>102</v>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3934,6 +3948,16 @@
       <c r="J57" t="n">
         <v>30</v>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4118,6 +4142,16 @@
       <c r="J61" t="n">
         <v>10</v>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4149,6 +4183,16 @@
       <c r="J62" t="n">
         <v>7</v>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4180,6 +4224,16 @@
       <c r="J63" t="n">
         <v>6</v>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4888,7 +4942,7 @@
       <c r="J76" t="n">
         <v>5</v>
       </c>
-      <c r="O76" s="14" t="n"/>
+      <c r="O76" s="11" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4925,7 +4979,7 @@
       <c r="J77" t="n">
         <v>0</v>
       </c>
-      <c r="O77" s="14" t="n"/>
+      <c r="O77" s="11" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4962,7 +5016,7 @@
       <c r="J78" t="n">
         <v>0</v>
       </c>
-      <c r="O78" s="14" t="n"/>
+      <c r="O78" s="11" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4999,7 +5053,7 @@
       <c r="J79" t="n">
         <v>6</v>
       </c>
-      <c r="O79" s="14" t="n"/>
+      <c r="O79" s="11" t="n"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5036,7 +5090,7 @@
       <c r="J80" t="n">
         <v>35</v>
       </c>
-      <c r="O80" s="14" t="n"/>
+      <c r="O80" s="11" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5073,7 +5127,7 @@
       <c r="J81" t="n">
         <v>8</v>
       </c>
-      <c r="O81" s="14" t="n"/>
+      <c r="O81" s="11" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5091,7 +5145,6 @@
           <t>Arewa 2</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5116,7 +5169,7 @@
       <c r="J82" t="n">
         <v>3</v>
       </c>
-      <c r="O82" s="14" t="n"/>
+      <c r="O82" s="11" t="n"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5134,7 +5187,6 @@
           <t>Darini Magaji Abu</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5159,7 +5211,7 @@
       <c r="J83" t="n">
         <v>12</v>
       </c>
-      <c r="O83" s="14" t="n"/>
+      <c r="O83" s="11" t="n"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5177,7 +5229,6 @@
           <t>Jamali</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5202,7 +5253,7 @@
       <c r="J84" t="n">
         <v>6</v>
       </c>
-      <c r="O84" s="14" t="n"/>
+      <c r="O84" s="11" t="n"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5220,7 +5271,6 @@
           <t>Mada</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -5245,25 +5295,3495 @@
       <c r="J85" t="n">
         <v>6</v>
       </c>
-      <c r="O85" s="14" t="n"/>
+      <c r="O85" s="11" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Abukur</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Rimi</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Bugaje</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Jibia; Katsina</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Dan Alhaji Yangayya</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Batsari; Jibia; Kurfi</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Gangara</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Batsari; Danja; Funtua; Jibia</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Maje Karare</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Charanchi; Rimi</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Makurda</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Kaita; Mani; Rimi</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Tsauri A</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Batsari; Kurfi</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Yandaki</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Jibia; Kaita; Katsina</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Yanhoho</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Kaita; Rimi</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Dan Alhaji Yangayya</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Batagarawa; Batsari; Kurfi</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Gabas 3</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Jino</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Batagarawa; Katsina</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Kwashabawa</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Rukudawa</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Batsari</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Yamma 2</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Yandaki</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Batagarawa; Kaita; Katsina</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Yau-Yau Malamawa</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Batsari</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Zuru</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Danragi</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Zuru</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Kyabu Kandu</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Wasagu/Danko</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Zuru</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Maza Maza</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Sakaba; Wasagu/Danko</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Zuru</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Yalmo Shindi Wari</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Wasagu/Danko</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Faru Magami</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Rabah</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Galadi</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Gandi 2</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Goronyo; Rabah</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Gangara</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Kalgo</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Kaya</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Mashema</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Rimawa</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Gada; Goronyo; Sabon Birni</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Sabon Gari Dole</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Goronyo; Rabah; Wurno</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Shanawa</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Tozai</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Gada; Illela; Sabon Birni</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Gangara</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Gilbadi</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Gada; Goronyo</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Rimawa</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Gada; Goronyo; Isa</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Tidibale</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Goronyo; Isa; Rabah</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Tozai</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Gada; Illela; Isa</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Tsabre</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Turba</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Yanfako</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Isa</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Balle</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Gudu</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Damba</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Gwadabawa; Illela</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Gidan Hamidu</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Kware; Wamako</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Gigane</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Gwadabawa; Illela</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Inname</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Binji</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Kalmalo</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Illela</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Kaura</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Wamako</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Marake</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Gudu</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Sabon Birni</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Gwadabawa; Kebbe; Kware; Sabon Birni; Tambuwal</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Samama</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Binji; Wamako</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Tudun Kose</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Binji</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Dansadau</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Gusau; Maru</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Faskari</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Magami</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Bungudu; Gusau; Maru</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Rijiya</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Bungudu; Gusau</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Sabon Layi</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Gusau</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Wanke</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Bungudu; Gusau</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Wonaka</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Birnin Magaji; Bungudu; Gusau</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Insecurity / conflict</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>WhatsApp/verbal (coordinator-transcribed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Yankara</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Yar Malamai</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Zango</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Newly added 2026-09-20 - this ward is Stage-1-eligible for your coverage but had never had a cluster drawn in it by chance, so it was missing from your assignment list until now (a gap found and fixed today, see the accompanying email). Please review and report on it like any other row.</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="K2:K75 K76:K81 K82:K85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L75 L76:L81 L82:L85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P75 P76:P81 P82:P85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q75 Q76:Q81 Q82:Q85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="O76:O81 O82:O85" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today." type="date" operator="between">
-      <formula1>2026-07-01</formula1>
-      <formula2>2026-09-16</formula2>
+    <dataValidation sqref="O2:O146" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date">
+      <formula1>2026-7-1</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5280,97 +8800,95 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O129"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="14" customWidth="1" style="11" min="1" max="1"/>
-    <col width="14" customWidth="1" style="11" min="2" max="2"/>
-    <col width="16" customWidth="1" style="11" min="3" max="3"/>
-    <col width="14" customWidth="1" style="11" min="4" max="4"/>
-    <col width="14" customWidth="1" style="11" min="5" max="5"/>
-    <col width="16" customWidth="1" style="11" min="6" max="6"/>
-    <col width="24" customWidth="1" style="11" min="7" max="7"/>
-    <col width="15" customWidth="1" style="11" min="8" max="8"/>
-    <col width="20" customWidth="1" style="11" min="9" max="9"/>
-    <col width="19" customWidth="1" style="11" min="10" max="10"/>
-    <col width="16" customWidth="1" style="11" min="11" max="11"/>
-    <col width="30" customWidth="1" style="11" min="12" max="12"/>
-    <col width="17" customWidth="1" style="11" min="13" max="13"/>
-    <col width="30" customWidth="1" style="11" min="14" max="14"/>
-    <col width="18" customWidth="1" style="11" min="15" max="15"/>
+    <col width="14" customWidth="1" style="13" min="1" max="2"/>
+    <col width="16" customWidth="1" style="13" min="3" max="3"/>
+    <col width="14" customWidth="1" style="13" min="4" max="5"/>
+    <col width="16" customWidth="1" style="13" min="6" max="6"/>
+    <col width="24" customWidth="1" style="13" min="7" max="7"/>
+    <col width="15" customWidth="1" style="13" min="8" max="8"/>
+    <col width="20" customWidth="1" style="13" min="9" max="9"/>
+    <col width="19" customWidth="1" style="13" min="10" max="10"/>
+    <col width="16" customWidth="1" style="13" min="11" max="11"/>
+    <col width="30" customWidth="1" style="13" min="12" max="12"/>
+    <col width="17" customWidth="1" style="13" min="13" max="13"/>
+    <col width="30" customWidth="1" style="13" min="14" max="14"/>
+    <col width="18" customWidth="1" style="13" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>LGA</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Ward (GRID3)</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Pop Type</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Cluster ID</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>IDP Category</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Target HHs (primary)</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Reserve HHs</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>Accessible (Y/N)</t>
         </is>
       </c>
-      <c r="J1" s="13" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Reason category</t>
         </is>
       </c>
-      <c r="K1" s="13" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>Reason notes</t>
         </is>
       </c>
-      <c r="L1" s="13" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>% of target achieved so far</t>
         </is>
       </c>
-      <c r="M1" s="13" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>Date reported</t>
         </is>
       </c>
-      <c r="N1" s="13" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>Reported by (Partner / IMPACT-default)</t>
         </is>
       </c>
-      <c r="O1" s="13" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>Source channel</t>
         </is>
@@ -9555,6 +13073,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9595,6 +13118,11 @@
       <c r="H112" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -10560,13 +14088,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C1B22D4-2D81-4DDD-8168-29144C8B46FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64861655-DFAE-4BF7-B0D1-95DC62E8FC0E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{022A4780-DB3B-4EA7-AEE3-4819D9B8F562}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD2DDE74-6005-4EFB-8ACB-B388F8CC3D28}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{270225AC-FE5D-4E9A-A39A-A497E42665CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C989786-B916-4C63-A547-145A9EE57F09}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/IRC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/IRC_accessibility_report.xlsx
@@ -235,8 +235,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O129" headerRowCount="1">
-  <autoFilter ref="A1:O129"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O179" headerRowCount="1">
+  <autoFilter ref="A1:O179"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -8799,7 +8799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O129"/>
+  <dimension ref="A1:O179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="13" min="1" max="2"/>
@@ -13810,18 +13810,1962 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Zuru</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Bedi</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>non_idp_NG022021_supp1</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Zuru</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Manga Ushe</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>non_idp_NG022021_supp2</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Zuru</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Bedi</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>non_idp_NG022021_supp3</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>non_idp_NG034019_supp1</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>non_idp_NG034019_supp3</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Jamali</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>non_idp_NG034019_supp4</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Salewa</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>non_idp_NG034019_supp5</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Gidan Madi</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>non_idp_NG034019_supp6</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>non_idp_NG034019_supp7</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Kusa</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>non_idp_NG021016_supp1</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Bugaje</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>non_idp_NG021016_supp2</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Darini Magaji Abu</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>non_idp_NG021016_supp3</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Bugaje</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>non_idp_NG021016_supp4</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Bugaje</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>non_idp_NG021016_supp5</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Arewa 2</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>non_idp_NG021016_supp6</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Kusa</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>non_idp_NG021016_supp7</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Darini Magaji Abu</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>non_idp_NG021016_supp8</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Tsafe Central</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp1</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Tsafe Central</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp10</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Tsafe Central</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp11</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Keta</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp12</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Keta</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp13</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Keta</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp3</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Tsafe Central</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp4</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Yankuzo B</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp5</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Keta</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp6</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Tsafe Central</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp7</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Tsanni</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>non_idp_NG021002_supp1</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Mada</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp16</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Tsafe Central</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp17</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Keta</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp18</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Ajiwa</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>non_idp_NG021002_supp2</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Tsanni</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>non_idp_NG021002_supp3</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Barawa</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>non_idp_NG021002_supp4</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Zuru</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Senchi</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>non_idp_NG022021_supp4</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Kebbi</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Zuru</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Senchi</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>non_idp_NG022021_supp5</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Salewa</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>non_idp_NG034019_supp8</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>non_idp_NG034019_supp9</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>non_idp_NG034019_supp10</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>idp_NG021002_supp1</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Dandagoro</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>idp_NG021002_supp2</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Dandagoro</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>idp_NG021002_supp3</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Batagarawa</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Dandagoro</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>idp_NG021002_supp4</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Kusa</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>idp_NG021016_supp1</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Katsina</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Jibia</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Kusa</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>idp_NG021016_supp2</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>idp_NG034019_supp1</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>idp_NG034019_supp2</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>idp_NG034019_supp3</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>idp_NG034019_supp4</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Sokoto</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Tangaza</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>IDP</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>idp_NG034019_supp5</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>In-host</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="I2:I129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14088,13 +16032,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64861655-DFAE-4BF7-B0D1-95DC62E8FC0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCF150FC-21C2-4334-9D28-4D3B4370547B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD2DDE74-6005-4EFB-8ACB-B388F8CC3D28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4534CCCF-E599-4838-B16F-0B56E6D397DA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C989786-B916-4C63-A547-145A9EE57F09}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C0DE45F-3D90-4AD4-9727-9050E236DCB3}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/IRC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/IRC_accessibility_report.xlsx
@@ -235,8 +235,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O179" headerRowCount="1">
-  <autoFilter ref="A1:O179"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O180" headerRowCount="1">
+  <autoFilter ref="A1:O180"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -8799,7 +8799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O179"/>
+  <dimension ref="A1:O180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="13" min="1" max="2"/>
@@ -13836,7 +13836,6 @@
           <t>non_idp_NG022021_supp1</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>6</t>
@@ -13874,7 +13873,6 @@
           <t>non_idp_NG022021_supp2</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
           <t>6</t>
@@ -13912,7 +13910,6 @@
           <t>non_idp_NG022021_supp3</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
           <t>6</t>
@@ -13950,7 +13947,6 @@
           <t>non_idp_NG034019_supp1</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
           <t>6</t>
@@ -13988,7 +13984,6 @@
           <t>non_idp_NG034019_supp3</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
           <t>6</t>
@@ -14026,7 +14021,6 @@
           <t>non_idp_NG034019_supp4</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>6</t>
@@ -14064,7 +14058,6 @@
           <t>non_idp_NG034019_supp5</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>6</t>
@@ -14102,7 +14095,6 @@
           <t>non_idp_NG034019_supp6</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>6</t>
@@ -14140,7 +14132,6 @@
           <t>non_idp_NG034019_supp7</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
           <t>6</t>
@@ -14178,7 +14169,6 @@
           <t>non_idp_NG021016_supp1</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>6</t>
@@ -14216,7 +14206,6 @@
           <t>non_idp_NG021016_supp2</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>6</t>
@@ -14254,7 +14243,6 @@
           <t>non_idp_NG021016_supp3</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>6</t>
@@ -14292,7 +14280,6 @@
           <t>non_idp_NG021016_supp4</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
           <t>6</t>
@@ -14330,7 +14317,6 @@
           <t>non_idp_NG021016_supp5</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>6</t>
@@ -14368,7 +14354,6 @@
           <t>non_idp_NG021016_supp6</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>6</t>
@@ -14406,7 +14391,6 @@
           <t>non_idp_NG021016_supp7</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
           <t>6</t>
@@ -14444,7 +14428,6 @@
           <t>non_idp_NG021016_supp8</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
           <t>6</t>
@@ -14482,7 +14465,6 @@
           <t>non_idp_NG037013_supp1</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
           <t>6</t>
@@ -14520,7 +14502,6 @@
           <t>non_idp_NG037013_supp10</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
           <t>6</t>
@@ -14558,7 +14539,6 @@
           <t>non_idp_NG037013_supp11</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
           <t>6</t>
@@ -14596,7 +14576,6 @@
           <t>non_idp_NG037013_supp12</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
           <t>6</t>
@@ -14634,7 +14613,6 @@
           <t>non_idp_NG037013_supp13</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
           <t>6</t>
@@ -14672,7 +14650,6 @@
           <t>non_idp_NG037013_supp3</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
           <t>6</t>
@@ -14710,7 +14687,6 @@
           <t>non_idp_NG037013_supp4</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
           <t>6</t>
@@ -14748,7 +14724,6 @@
           <t>non_idp_NG037013_supp5</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
           <t>6</t>
@@ -14786,7 +14761,6 @@
           <t>non_idp_NG037013_supp6</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
           <t>6</t>
@@ -14824,7 +14798,6 @@
           <t>non_idp_NG037013_supp7</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
           <t>6</t>
@@ -14862,7 +14835,6 @@
           <t>non_idp_NG021002_supp1</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
           <t>6</t>
@@ -14900,7 +14872,6 @@
           <t>non_idp_NG037013_supp16</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
           <t>6</t>
@@ -14938,7 +14909,6 @@
           <t>non_idp_NG037013_supp17</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
           <t>6</t>
@@ -14976,7 +14946,6 @@
           <t>non_idp_NG037013_supp18</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
           <t>6</t>
@@ -15014,7 +14983,6 @@
           <t>non_idp_NG021002_supp2</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
           <t>6</t>
@@ -15052,7 +15020,6 @@
           <t>non_idp_NG021002_supp3</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
           <t>6</t>
@@ -15090,7 +15057,6 @@
           <t>non_idp_NG021002_supp4</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
           <t>6</t>
@@ -15128,7 +15094,6 @@
           <t>non_idp_NG022021_supp4</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
           <t>6</t>
@@ -15166,7 +15131,6 @@
           <t>non_idp_NG022021_supp5</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
           <t>6</t>
@@ -15204,7 +15168,6 @@
           <t>non_idp_NG034019_supp8</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
           <t>6</t>
@@ -15242,7 +15205,6 @@
           <t>non_idp_NG034019_supp9</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
           <t>6</t>
@@ -15280,7 +15242,6 @@
           <t>non_idp_NG034019_supp10</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
           <t>6</t>
@@ -15754,18 +15715,56 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Zamfara</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Tsafe</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Keta</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Non-IDP</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>non_idp_NG037013_supp14</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="I2:I179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I180" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J180" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N180" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O180" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15774,271 +15773,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
-    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
-    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCF150FC-21C2-4334-9D28-4D3B4370547B}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4534CCCF-E599-4838-B16F-0B56E6D397DA}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C0DE45F-3D90-4AD4-9727-9050E236DCB3}"/>
 </file>
--- a/resampling/input/accessibility_reports_returned/IRC_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_returned/IRC_accessibility_report.xlsx
@@ -15773,4 +15773,271 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064B5BF8B0F90A143B1A4ACAD04008153" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada0274d0d067bbbdece3301958c05ce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="30973102-2308-455b-8e1f-b6a90edc3b23" xmlns:ns3="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f05eaaac1f596f0cf4554f8e9f637ce" ns2:_="" ns3:_="">
+    <xsd:import namespace="30973102-2308-455b-8e1f-b6a90edc3b23"/>
+    <xsd:import namespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="30973102-2308-455b-8e1f-b6a90edc3b23" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="12" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="13" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{daf5bdda-bc47-491d-9935-b3e42d5c0ae4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="947c1918-d5ab-48a1-8b61-0d52f2f99fd1">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="19" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="20" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="30973102-2308-455b-8e1f-b6a90edc3b23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="947c1918-d5ab-48a1-8b61-0d52f2f99fd1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53CF04FE-12F8-488D-B546-00C4DAF6F81E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D854874-072C-4C79-A73F-9BF517589B23}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49C90D04-EE56-4A23-95CE-6867D9B28CDC}"/>
 </file>